--- a/haver/haver-api_CPI/tickers.xlsx
+++ b/haver/haver-api_CPI/tickers.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4484"/>
+  <dimension ref="A1:B4487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36292,6 +36292,42 @@
       </c>
       <c r="B4484" t="inlineStr"/>
     </row>
+    <row r="4485">
+      <c r="A4485" t="inlineStr">
+        <is>
+          <t>H023PCX@G10</t>
+        </is>
+      </c>
+      <c r="B4485" t="inlineStr">
+        <is>
+          <t>G10 Core CPI</t>
+        </is>
+      </c>
+    </row>
+    <row r="4486">
+      <c r="A4486" t="inlineStr">
+        <is>
+          <t>H132PCX@G10</t>
+        </is>
+      </c>
+      <c r="B4486" t="inlineStr">
+        <is>
+          <t>G10 Core CPI</t>
+        </is>
+      </c>
+    </row>
+    <row r="4487">
+      <c r="A4487" t="inlineStr">
+        <is>
+          <t>H134PCX@G10</t>
+        </is>
+      </c>
+      <c r="B4487" t="inlineStr">
+        <is>
+          <t>G10 Core CPI</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
